--- a/promles.xlsx
+++ b/promles.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP54"/>
+  <dimension ref="A1:AP75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -9965,6 +9965,3135 @@
       <c r="AP54" t="inlineStr">
         <is>
           <t>2026-09-24T12:11:03+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1172441200</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Дрова кругляк 6 м, береза и хвоя, самовывоз</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Сортимент шесть метров, порода смешанная: хвоя и береза в одном штабеле. Лежит в Салыме, отгружаем с места.&lt;br&gt;&lt;br&gt;Лесу полтора года, все это время под открытым небом. Свежей рубки тут нет, вес уже не тот, что у зеленого леса. По влаге куча неровная: с краю и сверху бревно суше, в середине и снизу сырее, сверху шли дожди и снег. Приезжайте, разрубите полено и посмотрите сами, что берете. Долежать под навесом ему надо меньше, чем свежаку.&lt;br&gt;&lt;br&gt;Забирают самовывозом. Заезд твердый, лесовоз встает под погрузку в любую погоду, кран работает с площадки.&lt;br&gt;&lt;br&gt;Бумаги делаем полностью. Сделка идет через ФГИС ЛК, на груз выписываем ЭСД, куар код водитель получает на каждый рейс.&lt;br&gt;&lt;br&gt;Наличие по штабелю двигается, актуальный остаток уточняйте звонком. Завозим регулярно.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/01_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/01_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/01_3.jpg</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский АО, Салым, ул. Молодёжная, 4</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB55" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:20:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>5375627214</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Хлысты под лежневку, 5000 кубов на площадке</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Площадка под Няганью, в наличии около 5000 кубов хлыстами. Это самый большой остаток из наших площадок.&lt;br&gt;&lt;br&gt;Форма отпуска: дерево целиком, без раскряжевки. Порода хвойная, идет примесь березы. Рубка двухлетней давности.&lt;br&gt;&lt;br&gt;Под настил такой лес берут охотно. Свежей валкой его уже не назвать, за два года дерево стало легче зеленого. Сразу оговорюсь про влагу. Штабель стоит под открытым небом и просыхает неровно: по краям и сверху заметно суше, ближе к середине сырее, дожди и снег свое добавляют. Цифр обещать не стану, лучше посмотреть на месте, разрубим любой ствол на выбор. Что держится твердо: гнили нет, ствол крепкий.&lt;br&gt;&lt;br&gt;Отпускаем от 200 кубов. Так устроены погрузка и учет на площадке, меньшими партиями просто не получается.&lt;br&gt;&lt;br&gt;Документы. Куар код едет с каждым рейсом, ЭСД готов до погрузки, а делянка и остаток числятся в ФГИС ЛК. Отгрузка с места, погрузка на нас.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/05_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/05_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/05_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/05_4.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/05_5.jpg</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский АО, Нягань, ул. Сибирская, 20</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB56" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>200</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:50:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:50:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>8907360865</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Дрова кругляк хлыстами, 1000 кубов в наличии</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Кругляк на дрова, около 1000 кубов лежит на площадке под Нефтеюганском.&lt;br&gt;Сургут отсюда в шестидесяти километрах, ближе всех прочих городов: лесовоз успевает сходить туда и обратно в одну смену.&lt;br&gt;&lt;br&gt;Порода смешанная, что валили, то и в штабеле: хвоя пополам с лиственным. Форма хлыст, размер под свою котельную либо под пилораму режете уже у себя. Древесине полтора года, свежей валки тут нет. Штабель стоит под открытым небом, поэтому влажность внутри него разная: по верху и по краям дерево подвяленное, к середине и понизу сырее. Приезжайте, вскроем любой ряд, посмотрите сами.&lt;br&gt;&lt;br&gt;Стоит лес у кустовой площадки, рядом промысловая дорога с отсыпкой. Держит машину в любой сезон, распутица отгрузку не останавливает, ждать зимника не надо.&lt;br&gt;&lt;br&gt;Забор с места, транспорт ваш, погрузку делаем своей техникой и отдельно за неё не считаем.&lt;br&gt;&lt;br&gt;Бумаги: объём проведён по ФГИС ЛК, ЭСД оформляем к каждому рейсу, куар водитель получает перед выездом. На посту не держат.&lt;br&gt;&lt;br&gt;Берут котельные, дровяники, небольшие пилорамы. Звоните, по телефону уточню, сколько сейчас в штабеле, и поставим вас в график.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/13_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/13_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/13_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/13_4.jpg</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский автономный округ — Югра, Сургут, ул. Индустриальная, 22</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB57" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>2026-09-15T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>2026-10-15T11:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>9886960622</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Пиловочник сосна и кедр от 18 см, с места</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Сосна и кедр, деловая древесина своей заготовки. Кедр идёт хлыстами, сосна хлыстами и в раскряжёвке под заказ.&lt;br&gt;&lt;br&gt;Пиловочник от 18 см по вершинному отрезу, есть и толще. Ствол ровный, сбег небольшой. Лес лежит под открытым небом, поэтому за всю партию ручаться не стану: смотрим при отгрузке, брак в машину не кладём. Гниль отбраковываем прямо на раскряжёвке.&lt;br&gt;&lt;br&gt;Отдельной кучей лежит тонкомер. Это баланс, берут его целлюлозники и плитный завод. Пилораме он не нужен, а под свою задачу уходит хорошо.&lt;br&gt;&lt;br&gt;Документы: лес учтён в ФГИС ЛК, на отгрузку оформляем ЭСД и куар, водитель уезжает с полным комплектом.&lt;br&gt;&lt;br&gt;Отпуск с площадки, погрузка наша. Звоните и говорите сразу, что за станок и какая длина нужна, подберём из того, что лежит. Приезжайте, покажу штабель до погрузки.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/17_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/17_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/17_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/17_4.jpg</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский АО, Урай, ул. Шевченко, 30</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB58" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>180</v>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>2026-09-15T17:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>2026-10-15T15:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>6109654175</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Древесина дровяная 6 м, отпуск от машины</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>До Увата от нашей площадки порядка 180 километров асфальта по трассе на Ханты-Мансийск. Дорога рабочая круглый год, зимника ждать не нужно.&lt;br&gt;&lt;br&gt;Что берете: кругляк длиной 6 м, хвойные вперемешку с березой. Штабелю полтора года, стоял на улице. Это не вчерашняя валка, бревно ощутимо легче зеленого, но сухим назвать его я не могу: верх подвялило, низ и нутро остались с влагой. Кому в котел, тем лучше глянуть вживую и выбрать, что подойдет.&lt;br&gt;&lt;br&gt;Порядок такой. Подъехали, осмотрели, определились с машиной, загрузились, ушли. Отпуск от машины, мельче не дробим.&lt;br&gt;&lt;br&gt;Оформление до выезда: партия проходит ФГИС ЛК, на груз выдается электронный сопроводительный документ ЭСД, куар под каждую ходку водителю в кабину.&lt;br&gt;&lt;br&gt;Свободный остаток плавает, точную картину скажем по телефону. Пополнение идет постоянно.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/02_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/02_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/02_3.jpg</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Тюменская обл., Уват, ул. Ленина, 63</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB59" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>2026-09-16T05:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>2026-10-16T03:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>8930305414</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Лес на лежневку хлыстами, отпуск от 200 кубов</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>До Югорска от площадки под Няганью около 90 км по трассе, плечо короткое, лесовоз оборачивается за день.&lt;br&gt;&lt;br&gt;Лежит порядка 5000 кубов хлыста. Хвоя, местами береза, ствол цельный, на сортимент резать не станем.&lt;br&gt;&lt;br&gt;Если закрываете лежневую дорогу, картина такая. Лес с рубки стоит два года, это не свежак, и он легче зеленого. Насколько именно легче, сказать не берусь: верхние ряды обветрило, внутри штабеля держится вода. По влажности честнее смотреть своими глазами, за этим и зовем на площадку, вскроем ряд в любом месте. Гнили нет, ствол крепкий, на настил идет нормально. Часть объема уходит на дрова.&lt;br&gt;&lt;br&gt;Минимальная отгрузка 200 кубов. Причина простая: площадка грузит и считает крупными партиями, под такой ритм собрана техника.&lt;br&gt;&lt;br&gt;С бумагами вопросов не будет. Объем стоит в ФГИС ЛК, перед выездом машины готовим ЭСД, куар водитель везет при себе.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/06_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/06_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/06_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/06_4.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/06_5.jpg</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский АО, Югорск, ул. Промышленная, 3</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB60" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
+        <v>200</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>2026-09-16T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>2026-10-16T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>8244374875</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Лес хлыстами на лежневку, заезд для американца</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Хлысты под лежнёвку, порядка 1000 кубов, своя площадка под самим Нефтеюганском, у кустовой.&lt;br&gt;Главное здесь заезд: к штабелю подходит американец, седельный тягач с прицепом.&lt;br&gt;&lt;br&gt;История знакомая: лес найти можно, а подобраться к нему выходит только зимой, летом дорога раскисает и вывоз встаёт. С этой площадкой проще. Промысловая дорога отсыпана, идёт прямо к штабелю и работает круглый год. Американец машина тяжёлая, сцепка длинная, к дороге она требовательнее прочих. Раз проходит он, значит обычный лесовоз пройдёт тем более, хоть в мае, хоть в октябре. Разворот у штабеля просторный, встать под погрузку получается спокойно, приезжайте когда вам удобно.&lt;br&gt;&lt;br&gt;Лес лежит здесь же, под городом, везти его к вам издалека не нужно. Приехали, посмотрели штабель, замерили, загрузились в тот же день.&lt;br&gt;&lt;br&gt;По фактуре: породы смешанные, форма хлыст, лежит полтора года, валка не свежая. Штабель под открытым небом, влага в нём распределена неровно, для такого хранения это обычное дело. На настил материал рабочий, дорожники берут его регулярно, остаток уходит на дрова.&lt;br&gt;&lt;br&gt;Документы: ФГИС ЛК, ЭСД на каждую машину, куар на рейс.&lt;br&gt;&lt;br&gt;Дмитрий, ПромЛес. Наберите, согласуем время заезда.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/14_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/14_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/14_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/14_4.jpg</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский АО, Нефтеюганск, ул. Строителей, 7</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB61" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG61" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>2026-09-16T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>2026-10-16T11:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>9207257326</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Пиловочник кедровый хлыстами, есть балансы</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Кедр хлыстами, лежит в Урае, ХМАО. Цена с места, самовывоз машиной покупателя.&lt;br&gt;&lt;br&gt;До Челябинска около тысячи километров. Дорога накатанная, за кедром сюда ездят регулярно и грузятся под полную машину, чтобы плечо окупилось.&lt;br&gt;&lt;br&gt;Хлыст длинный, порезать можем на месте под нужную длину, скажите заранее. Хранение открытое, поэтому по синеве и по комлю лучше глянуть глазами: покажу партию перед погрузкой, отберём то, что подходит под распил.&lt;br&gt;&lt;br&gt;Рядом отсортирован хвойный тонкомер, он же баланс, под целлюлозу и плиту. Если производство берёт и то и другое, увозят одной ходкой.&lt;br&gt;&lt;br&gt;По бумагам: работаем в ФГИС ЛК, оформляем ЭСД, куар выдаётся на каждую поездку. Комплект водителю отдаём до выезда.&lt;br&gt;&lt;br&gt;Звоните, расскажу, что сейчас есть в наличии.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/18_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/18_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/18_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/18_4.jpg</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Челябинская обл., Челябинск, Копейское шоссе, 48</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Кедр</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB62" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>180</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG62" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>2026-09-16T17:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>2026-10-16T15:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>8648628361</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Дрова хлыстами хвоя, лежат вторую зиму</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Дрова хлыстами, хвоя с примесью березы. На площадке под Няганью около 5000 кубов, до Лыхмы порядка 200 км.&lt;br&gt;&lt;br&gt;Как идет сделка. Сначала созвон, называете объем и сроки. Дальше смотрите штабель на месте либо скидываем свежее фото и видео. Замеряете выборочно, вопросов по кубатуре потом не возникает. После этого заявка, оформление и погрузка.&lt;br&gt;&lt;br&gt;По состоянию скажу как есть. Дерево лежит с рубки два года, вторую зиму стоит на улице. Открытый штабель сохнет неодинаково: сверху и с боков сильнее, снизу и внутри дольше держит воду. Поэтому влагу правильнее оценивать на месте, вскроем ряд, посмотрите сами. Гнили нет, ствол крепкий. Раскряжевка и колка на стороне покупателя, отдаем целиком.&lt;br&gt;&lt;br&gt;Отгружаем партиями от 200 кубов. Столько обычно и берут под котельную, поселок или вахту.&lt;br&gt;&lt;br&gt;Бумаги закрываем полностью: учет в ФГИС ЛК, ЭСД на рейс, куар код на машину. Забор с места.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/07_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/07_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/07_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/07_4.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/07_5.jpg</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский АО, Лыхма, ул. Центральная, 5</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB63" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG63" t="n">
+        <v>200</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>2026-09-17T05:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>2026-10-17T03:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>6659548256</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Лес хлыстами под лежневку, сортировка на месте</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Хлысты лежат на площадке под Ураем, объём больше пяти тысяч кубов.&lt;br&gt;Породы смешанные, берёзу или сосну отбираем отдельно под заявку.&lt;br&gt;&lt;br&gt;Делянка домашняя, владелец работает на ней сам. Лес двух возрастов. Свежий, рубка этой зимы, его разбирают на пиловочник и под сруб. Двухгодовалый, срок лёжки вторая зима, его берут в лежнёвку и в дрова. Кедр тоже лежит. Влага в штабеле неровная, верх и края одно, середина другое, смотреть лучше на месте.&lt;br&gt;&lt;br&gt;Порядок простой. Звонок, называете породу и объём, приезжаете смотреть. Отбор делаем до погрузки, прямо на площадке. Сказали берёзу, грузим берёзу. Нужна сосна, откладываем сосну. Что заказали, то и уедет в кузове.&lt;br&gt;&lt;br&gt;Подъездные пути твёрдые, лесовоз с прицепом заходит круглый год. Площадка открытая, развернуться есть где.&lt;br&gt;&lt;br&gt;Документы оформляются полностью: ФГИС ЛК, ЭСД на машину, куар на рейс. Водитель проходит пост без задержки.&lt;br&gt;&lt;br&gt;Отпуск с места, самовывоз.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/09_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/09_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/09_3.jpg</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский АО, Урай, ул. Узбекистанская, 8</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB64" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>2026-09-17T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>2026-10-17T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>3937137168</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Лес дровяной хлыстами, подъезд круглый год</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Тысяча кубов дровяного леса в штабеле, площадка под Нефтеюганском. Порода смешанная, лежит хлыстами.&lt;br&gt;Плечо до Лангепаса около 220 километров, направление рабочее, лесовозы ходят по нему постоянно.&lt;br&gt;&lt;br&gt;Скажу честно про состояние. Древесине полтора года, это не свежая рубка. Но сушкой я это называть не стану: над штабелем дожди и снег, сверху дерево подвялилось, а глубже осталось сырым. Что там по влаге, честнее смотреть глазами на месте, подъезжайте и разрубите любой ствол, какой выберете.&lt;br&gt;&lt;br&gt;Внутри штабеля хвойный и лиственный кругляк вперемешку, диаметр рабочий. Режете под свой размер сами, хоть под котельную, хоть на продажу населению.&lt;br&gt;&lt;br&gt;Подъезд отсыпанный, идёт от промысловой дороги. Сезон роли не играет, заехать можно и в апреле, техника у штабеля стоит твёрдо.&lt;br&gt;&lt;br&gt;Вывоз с места, машины ваши, грузим сами.&lt;br&gt;&lt;br&gt;По бумагам чисто: партия учтена во ФГИС ЛК, на отгрузку оформляется ЭСД, куар уходит вместе с водителем.&lt;br&gt;&lt;br&gt;Часть объёма забирают под лежнёвку, но основная линия здесь дрова. Наберите, скажу, сколько ещё осталось.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/15_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/15_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/15_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/15_4.jpg</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский АО, Лангепас, ул. Солнечная, 15</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB65" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG65" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>2026-09-17T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>2026-10-17T11:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2812419332</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник от 18 см, баланс в наличии</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Сосна на пилораму, отгрузка из Урая в ХМАО. Стоимость указана на площадке, забирают своим транспортом.&lt;br&gt;&lt;br&gt;Как проходит сделка. Сначала созвон: называете сортимент, длину и объём под свой станок. Дальше приезжает водитель или представитель, смотрит штабель, меряет вершину рулеткой, на слово ничего принимать не нужно. Если что-то в партии не устраивает, отложим и подберём другое. Потом загрузка нашей техникой, машина уходит в тот же день.&lt;br&gt;&lt;br&gt;От Тюмени до нас порядка семисот километров по трассе. Рейс рядовой, лесовозы этим маршрутом ходят круглый год, возить выгодно полным кузовом.&lt;br&gt;&lt;br&gt;Толщина по верхнему отрезу начинается с восемнадцати сантиметров. Сосна боровая, хранится на открытой площадке, состояние ствола смотрим вместе при отборе. Тонкомер отложен отдельно, уходит балансом в переработку.&lt;br&gt;&lt;br&gt;Сопровождение сделки через ФГИС ЛК, к отгрузке готовим ЭСД с куаром на рейс.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/19_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/19_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/19_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/19_4.jpg</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Тюменская обл., Тюмень, ул. Судостроителей, 1</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB66" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>180</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG66" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>2026-09-17T17:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>2026-10-17T15:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>7926555961</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Кругляк 6 м под лежневку и настил, опт</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Снабженцам и прорабам, кто закрывает лежневку на кустах и зимние проезды. Кругляк шестиметровый, лес смешанный, хвоя с березой. Штабель в Салыме, от Нефтеюганска сотня километров по асфальту, машина оборачивается за день.&lt;br&gt;&lt;br&gt;Под настил эта длина удобная: ложится поперек полотна ровно, меньше остатков при раскладке. Древесина лежалая, полтора года на воздухе, часть влаги ушла, пачка весит меньше свежесрубленной. Насквозь просохнуть она не могла, внутри бревно сырее, под настил это роли не играет.&lt;br&gt;&lt;br&gt;Основание площадки твердое, лесовоз заходит и разворачивается, грузим прямо от штабеля. Опт, минимум одна машина, дальше по потребности объекта.&lt;br&gt;&lt;br&gt;Лес учтенный: декларации идут через систему ФГИС ЛК, на отправку оформляется ЭСД, куар на рейс уезжает вместе с водителем.&lt;br&gt;&lt;br&gt;Сколько лежит сейчас, скажем по звонку. Подъехать и посмотреть можно в любой день.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/03_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/03_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/03_3.jpg</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский АО, Нефтеюганск, 11 микрорайон, 24</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB67" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG67" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>2026-09-18T05:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>2026-10-18T03:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>7563548962</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Древесина на дрова хлыстами, крупный объем</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Около 5000 кубов дровяного хлыста, самый крупный из моих остатков. В Ханты-Мансийск дорога порядка 250 км от площадки под Няганью.&lt;br&gt;&lt;br&gt;Расскажу, откуда лес. Валили два года назад, часть тогда ушла заказчику под дорогу, остальное так и стоит в штабелях. Две зимы на воздухе даром не прошли, свежей рубкой это дерево уже не является. Полностью сухим я его тоже не назову: верх обветрился, низ и середина сырее, сверху ложится снег. Кому важна влажность, приезжайте до заявки, раскряжуем пару стволов и поглядите на срез. Гнили нет, ствол крепкий.&lt;br&gt;&lt;br&gt;Порода хвойная, попадается береза, ее часто просят отдельно. Отдаю целым деревом, пилить по метражу не берусь, у покупателя своей пилой обычно выходит дешевле.&lt;br&gt;&lt;br&gt;Работаю от 200 кубов. Размер такой потому, что площадка живет сезонными заявками, для котельной или поселка это привычная цифра.&lt;br&gt;&lt;br&gt;По учету так: весь объем в ФГИС ЛК, на выезд готовится ЭСД, куар код прикладываем к рейсу. Отгружаем с площадки.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/08_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/08_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/08_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/08_4.jpg</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский автономный округ — Югра, Ханты-Мансийск, ул. Промышленная, 17</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB68" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG68" t="n">
+        <v>200</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>2026-09-18T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>2026-10-18T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2203575485</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Кругляк сосна и береза хлыстами с делянки</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Кругляк хлыстами с делянки, на площадке свыше пяти тысяч кубов.&lt;br&gt;Отгрузка идёт из Урая, ХМАО. От Серова это порядка четырёхсот километров на север, цена указана с места.&lt;br&gt;&lt;br&gt;Сосна и берёза разбираются по породам. Партия собирается под конкретного заказчика: нужен чистый сосновый кругляк, отложим сосну, нужна одна берёза, наберём берёзу. Кедр в наличии.&lt;br&gt;&lt;br&gt;Лес лежит разного срока. То, что рублено зимой, свежее, его берут в пиловочник и на сруб. То, что отстояло два года, ровно ложится в лежнёвку под технику. Про влагу скажу как есть: навеса над лесом нет, дождь и снег бьют сверху, отсюда разница между краем пачки и её серединой. Приезжайте, раскряжуем при вас и всё будет видно.&lt;br&gt;&lt;br&gt;Дорога к штабелям держит лесовоз с прицепом, зимника ждать не надо, заезд рабочий весь год.&lt;br&gt;&lt;br&gt;По бумагам чисто. Весь объём стоит на учёте в ФГИС ЛК, там же закрывается сделка. Водителю в кабину кладётся ЭСД. Под рейс отдельно генерируется куар, его и показывают при проверке.&lt;br&gt;&lt;br&gt;Самовывоз. Объём позволяет закрыть крупную заявку за один заход.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/10_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/10_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/10_3.jpg</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Свердловская обл., Серов, ул. Заславского, 25</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB69" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG69" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>2026-10-18T11:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>7806886486</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Кедр пиловочник хлыстами, отгрузка из Урая</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Кедр пиловочник, заготовка собственная. Лес стоит на площадке в Урае, ХМАО, цена назначена с места, увозят самовывозом.&lt;br&gt;&lt;br&gt;Делянку рубим сами, кедр брали в сухом бору. Лежит всё под небом, так что обещать за каждый ствол не буду: приезжайте, раскатаем штабель и посмотрим вместе, что берёте. Отпускается хлыстами, длина полная, раскряжёвку делаем по запросу.&lt;br&gt;&lt;br&gt;Бумаги закрыты целиком: учёт в ФГИС ЛК, декларация о сделке, ЭСД и куар на рейс. Копии водитель получает на руки перед выездом с территории.&lt;br&gt;&lt;br&gt;Екатеринбург от нас примерно восемьсот километров. Плечо привычное, оттуда машины приходят постоянно, вопрос один: не гонять кузов полупустым. Кедр южнее найти сложнее, потому и едут на север.&lt;br&gt;&lt;br&gt;Есть также сосна и хвойный тонкомер под баланс, если нужно добрать объём. Звоните, подскажу по срокам.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/20_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/20_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/20_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/20_4.jpg</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Свердловская обл., Екатеринбург, ул. Кирпичная, 5</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Кедр</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB70" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>180</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG70" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>2026-09-18T17:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>2026-10-18T15:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>6854785666</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Бревно 6 м на лежневку, лес смешанных пород</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Заготовка своя, лес с собственной делянки. Бревно шестиметровое, хвойные и береза вместе. Площадка стоит в Салыме, до Тобольска около 280 км по асфальтированной дороге.&lt;br&gt;&lt;br&gt;Документы веду сразу, не задним числом. Сведения по партии уходят через ФГИС ЛК, водителю на руки ЭСД и куар код на любой выезд, его сканируют на посту.&lt;br&gt;&lt;br&gt;Берут материал под дорожные работы: лежневка, временные настилы, съезды, подсыпка слабых мест, площадки под технику. Полтора года пролежал на улице, от свежака отличается заметно. Ровной просушки на воздухе не бывает, дождь и снег делают свое: одно бревно подвяленное, соседнее с влагой внутри. Подъезжайте, покажу весь ряд, разберемся вместе.&lt;br&gt;&lt;br&gt;Грузим круглогодично, подъезд держит тяжелую машину, лесовоз становится вплотную к куче.&lt;br&gt;&lt;br&gt;Отпускаем от машины. Текущее наличие озвучу по телефону, звоните в рабочее время.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/04_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/04_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/04_3.jpg</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Тюменская обл., Тобольск, ул. Знаменского, 33</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB71" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG71" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>2026-09-19T05:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>2026-10-19T03:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>5820642127</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Дрова хлыстами сосна и береза с площадки</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Машина встаёт под погрузку на площадке под Ураем и уходит с полным кузовом.&lt;br&gt;Дрова хлыстами, берёза и сосна, в штабелях больше пяти тысяч кубов.&lt;br&gt;&lt;br&gt;От Ивделя ехать около трёхсот километров, направление северное. Отгрузка идёт из Урая, ценник стоит с места, забор своим транспортом.&lt;br&gt;&lt;br&gt;Про состояние честно. Часть леса стоит вторую зиму. Это срок лёжки, а не готовность полена к печи: под открытым небом верх мокнет от дождя и снега, внутри штабеля влага держится дольше. Состояние честнее посмотреть на месте, разрубим при вас. Другая часть свежая, зимней рубки, такую обычно забирают на пиловочник и в сруб, но и в топку она годится.&lt;br&gt;&lt;br&gt;Породу набираем до того, как подошёл автомобиль. Нужна чистая берёза, скажете в заявке и получите берёзу. По сосне так же. Кедр в общей массе есть.&lt;br&gt;&lt;br&gt;Качество ровное, гнили нет. Подъезд твёрдый, грузим быстро.&lt;br&gt;&lt;br&gt;Теперь про бумаги. Лес заведён в ФГИС ЛК, декларация закрыта. Перед выездом готовим сопроводительный документ ЭСД, он едет вместе с водителем. Куар формируется под конкретную машину, на посту его просто сканируют.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/11_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/11_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/11_3.jpg</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Свердловская обл., Ивдель, ул. Ворошилова, 4</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB72" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG72" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>2026-09-19T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>2026-10-19T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>8632928158</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Береза на дрова хлыстами, есть сосна и кедр</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Берёза на дрова хлыстами, рядом сосна, отдельно попадается кедр.&lt;br&gt;Площадка под Ураем, в штабелях за пять тысяч кубов.&lt;br&gt;&lt;br&gt;Делянка домашняя, хозяйская, её пилят не первый сезон. От Советского сюда примерно сто девяносто километров.&lt;br&gt;&lt;br&gt;Валили в два захода. Одна часть лежит вторую зиму, её чаще берут в печь и под лежнёвку. Сухой я её не называю: штабель под небом, влага внутри распределена неровно, край и середина отличаются. Вторая свежая, этой зимы, из неё тянут пиловочник и материал под сруб. Гниль не идёт, смотрели на раскряжёвке.&lt;br&gt;&lt;br&gt;Про отбор. Породу можно заказать заранее, руки на это есть. Назовёте берёзу, соберут берёзу. Попросите сосну, соберут сосну. Кедр при желании отберут отдельной пачкой.&lt;br&gt;&lt;br&gt;Дорога до штабелей нормальная, лесовоз проходит в любой месяц.&lt;br&gt;&lt;br&gt;Документация через ФГИС ЛК, оформляется ЭСД, куар выдаётся на рейс. Проверка на дороге вопросов не вызовет.&lt;br&gt;&lt;br&gt;Забирают самовывозом, цена с места. Звоните, договоримся о времени и покажу делянку.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/12_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/12_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/12_3.jpg</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский АО, Советский, ул. Гагарина, 26</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB73" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG73" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>2026-10-19T11:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1640018245</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Кругляк хлыстами на лежневку, отгрузка с места</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Кругляк хлыстами на лежнёвку, площадка под Нефтеюганском, ХМАО. Лежит тысяча кубов, отпуск прямо со штабеля.&lt;br&gt;До Когалыма примерно 200 километров, дорога накатанная.&lt;br&gt;&lt;br&gt;1. Порода: смешанная, хвойный и лиственный лес в одном штабеле.&lt;br&gt;2. Форма: хлыст, диаметр рабочий, идёт на настилы и временные проезды.&lt;br&gt;3. Состояние: полтора года на площадке, валка не свежая. Хранение открытое, влажность по штабелю неодинаковая, оценивать её лучше на месте.&lt;br&gt;4. Объём: порядка тысячи кубов, отдаём от лесовоза и до полного остатка.&lt;br&gt;5. Заезд: стоим у кустовой, рядом промысловая дорога с твёрдым покрытием, работаем без привязки к зимнику.&lt;br&gt;6. Погрузка: техника наша, стоит на месте, вывоз транспортом покупателя.&lt;br&gt;7. Бумаги: учёт во ФГИС ЛК, ЭСД на груз, куар на каждый выезд.&lt;br&gt;&lt;br&gt;Основной спрос на лежнёвку, остатки разбирают на дрова. Дмитрий, ПромЛес, звоните по объёму и графику отгрузки.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/16_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/16_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/16_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/16_4.jpg</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский АО, Когалым, ул. Дружбы Народов, 24</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB74" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>160</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG74" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL74" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>2026-10-19T15:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3603116761</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>79128885747</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Баланс хвойный и пиловочник, кедр и сосна</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Хвойный баланс объёмом, рядом деловой лес. Место погрузки Урай, ХМАО. Цена за лес на площадке, вывоз силами покупателя.&lt;br&gt;&lt;br&gt;Вопрос у переработки обычно один: сойдутся ли документы с грузом на весовой. Оформление держим на себе. Поставка идёт через ФГИС ЛК, электронный сопроводительный документ ЭСД готовим до выезда, куар приходит на каждую ходку.&lt;br&gt;&lt;br&gt;Тонкомер сортируем в свою кучу, он уходит на плиту и на варку целлюлозы. Деловую часть отбираем отдельно: сосна и кедр под распил, вершинный отруб крупный, годится на брус и на доску. Кедр чаще спрашивают под сруб и столярку.&lt;br&gt;&lt;br&gt;До Перми порядка девятисот километров. Для лесовоза это один длинный рейс, машину набиваем полностью, пустого места в кузове не оставляем.&lt;br&gt;&lt;br&gt;Подъезд твёрдый, работаем не только по зимнику, отпуск круглый год. Лес перед загрузкой осматривают спокойно, время на это даём.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/21_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/21_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/21_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/wave_2026-09-15/21_4.jpg</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Пермский край, Пермь, ул. Промышленная, 111</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Товар от производителя</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Кедр</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB75" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>180</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>От количества</t>
+        </is>
+      </c>
+      <c r="AG75" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Метр кубический</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>fesev22606@aspensif.com</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>ПромЛес</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>2026-09-20T05:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>2026-10-20T03:30:00+03:00</t>
         </is>
       </c>
     </row>
